--- a/2designs_codebook.xlsx
+++ b/2designs_codebook.xlsx
@@ -7141,7 +7141,7 @@
       </c>
       <c r="K2" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" s="9" t="inlineStr">
@@ -7209,7 +7209,7 @@
       <c r="F3" s="7" t="n"/>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
@@ -7249,17 +7249,17 @@
       </c>
       <c r="O3" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P3" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" s="10" t="inlineStr">
@@ -7297,7 +7297,7 @@
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
@@ -7395,12 +7395,12 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K5" s="9" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" s="10" t="inlineStr">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N6" s="9" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -7649,7 +7649,7 @@
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" s="10" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N10" s="9" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7913,12 +7913,12 @@
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="8" t="inlineStr">
@@ -7928,12 +7928,12 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -8001,7 +8001,7 @@
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="Q12" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R12" s="10" t="inlineStr">
@@ -8094,22 +8094,22 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" s="9" t="inlineStr">
@@ -8129,7 +8129,7 @@
       </c>
       <c r="O13" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="Q13" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R13" s="10" t="inlineStr">
@@ -8177,7 +8177,7 @@
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
@@ -8265,7 +8265,7 @@
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr">
@@ -8358,22 +8358,22 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr">
@@ -8383,27 +8383,27 @@
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O16" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P16" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R16" s="10" t="inlineStr">
@@ -8441,7 +8441,7 @@
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -8451,17 +8451,17 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -8481,17 +8481,17 @@
       </c>
       <c r="O17" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q17" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R17" s="10" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
@@ -8559,12 +8559,12 @@
       </c>
       <c r="M18" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
@@ -8627,17 +8627,17 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
@@ -8657,17 +8657,17 @@
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R19" s="10" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
@@ -8735,12 +8735,12 @@
       </c>
       <c r="M20" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O20" s="10" t="inlineStr">
@@ -8803,17 +8803,17 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -8833,17 +8833,17 @@
       </c>
       <c r="O21" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q21" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R21" s="10" t="inlineStr">
@@ -8891,12 +8891,12 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O22" s="10" t="inlineStr">
@@ -8969,7 +8969,7 @@
       <c r="F23" s="7" t="n"/>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="9" t="inlineStr">
@@ -9145,7 +9145,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -9233,7 +9233,7 @@
       <c r="F26" s="7" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L26" s="9" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L27" s="9" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L28" s="9" t="inlineStr">
@@ -9497,7 +9497,7 @@
       <c r="F29" s="7" t="n"/>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L29" s="9" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
@@ -9615,12 +9615,12 @@
       </c>
       <c r="M30" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O30" s="10" t="inlineStr">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K31" s="9" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="M31" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N31" s="9" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="O32" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P32" s="10" t="inlineStr">
@@ -9859,12 +9859,12 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K33" s="9" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="M33" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N33" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O33" s="10" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="M34" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N34" s="9" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10025,7 +10025,7 @@
       <c r="F35" s="7" t="n"/>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
@@ -10045,7 +10045,7 @@
       </c>
       <c r="K35" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L35" s="9" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="K36" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
@@ -10153,17 +10153,17 @@
       </c>
       <c r="O36" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P36" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R36" s="10" t="inlineStr">
@@ -10201,7 +10201,7 @@
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="M39" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N39" s="9" t="inlineStr">
@@ -10417,17 +10417,17 @@
       </c>
       <c r="O39" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q39" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R39" s="10" t="inlineStr">
@@ -10465,7 +10465,7 @@
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -10505,17 +10505,17 @@
       </c>
       <c r="O40" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P40" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R40" s="10" t="inlineStr">
@@ -10563,17 +10563,17 @@
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
@@ -10593,17 +10593,17 @@
       </c>
       <c r="O41" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q41" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R41" s="10" t="inlineStr">
@@ -10646,22 +10646,22 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L42" s="9" t="inlineStr">
@@ -10671,27 +10671,27 @@
       </c>
       <c r="M42" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N42" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O42" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P42" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q42" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R42" s="10" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K43" s="9" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="M43" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N43" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O43" s="10" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr">
@@ -10847,17 +10847,17 @@
       </c>
       <c r="M44" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N44" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O44" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P44" s="10" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R44" s="10" t="inlineStr">
@@ -10910,17 +10910,17 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr">
@@ -10935,12 +10935,12 @@
       </c>
       <c r="M45" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N45" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O45" s="10" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="Q45" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R45" s="10" t="inlineStr">
@@ -10993,7 +10993,7 @@
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -11033,17 +11033,17 @@
       </c>
       <c r="O46" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P46" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q46" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R46" s="10" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr">
@@ -11111,22 +11111,22 @@
       </c>
       <c r="M47" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N47" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O47" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P47" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q47" s="10" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -11179,17 +11179,17 @@
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L48" s="9" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="M48" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N48" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O48" s="10" t="inlineStr">
@@ -11257,7 +11257,7 @@
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
@@ -11277,7 +11277,7 @@
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L49" s="9" t="inlineStr">
@@ -11297,17 +11297,17 @@
       </c>
       <c r="O49" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q49" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R49" s="10" t="inlineStr">
@@ -11385,17 +11385,17 @@
       </c>
       <c r="O50" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P50" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q50" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R50" s="10" t="inlineStr">
@@ -11433,7 +11433,7 @@
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -11473,17 +11473,17 @@
       </c>
       <c r="O51" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P51" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q51" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R51" s="10" t="inlineStr">
@@ -11521,7 +11521,7 @@
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -11561,17 +11561,17 @@
       </c>
       <c r="O52" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P52" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q52" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R52" s="10" t="inlineStr">
@@ -11609,7 +11609,7 @@
       <c r="F53" s="7" t="n"/>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
@@ -11624,12 +11624,12 @@
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K53" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="O53" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q53" s="10" t="inlineStr">
@@ -11712,12 +11712,12 @@
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" s="9" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="O54" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P54" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q54" s="10" t="inlineStr">
@@ -11785,7 +11785,7 @@
       <c r="F55" s="7" t="n"/>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
@@ -11825,17 +11825,17 @@
       </c>
       <c r="O55" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q55" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R55" s="10" t="inlineStr">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L56" s="9" t="inlineStr">
@@ -11913,17 +11913,17 @@
       </c>
       <c r="O56" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P56" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q56" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R56" s="10" t="inlineStr">
@@ -11961,7 +11961,7 @@
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -12001,17 +12001,17 @@
       </c>
       <c r="O57" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q57" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R57" s="10" t="inlineStr">
@@ -12064,12 +12064,12 @@
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L58" s="9" t="inlineStr">
@@ -12089,17 +12089,17 @@
       </c>
       <c r="O58" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P58" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q58" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R58" s="10" t="inlineStr">
@@ -12152,12 +12152,12 @@
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K59" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L59" s="9" t="inlineStr">
@@ -12177,12 +12177,12 @@
       </c>
       <c r="O59" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q59" s="10" t="inlineStr">
@@ -12240,7 +12240,7 @@
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
@@ -12255,27 +12255,27 @@
       </c>
       <c r="M60" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N60" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O60" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q60" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R60" s="10" t="inlineStr">
@@ -12285,7 +12285,7 @@
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12328,12 +12328,12 @@
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K61" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="M61" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N61" s="9" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="O61" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P61" s="10" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="Q61" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R61" s="10" t="inlineStr">
@@ -12406,17 +12406,17 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr">
@@ -12431,27 +12431,27 @@
       </c>
       <c r="M62" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N62" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O62" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P62" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q62" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R62" s="10" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12489,7 +12489,7 @@
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -12529,17 +12529,17 @@
       </c>
       <c r="O63" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q63" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R63" s="10" t="inlineStr">
@@ -12587,12 +12587,12 @@
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr">
@@ -12607,22 +12607,22 @@
       </c>
       <c r="M64" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O64" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P64" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q64" s="10" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="S64" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12665,7 +12665,7 @@
       <c r="F65" s="7" t="n"/>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
@@ -12685,7 +12685,7 @@
       </c>
       <c r="K65" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L65" s="9" t="inlineStr">
@@ -12705,17 +12705,17 @@
       </c>
       <c r="O65" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P65" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q65" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R65" s="10" t="inlineStr">
@@ -12763,17 +12763,17 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L66" s="9" t="inlineStr">
@@ -12783,27 +12783,27 @@
       </c>
       <c r="M66" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N66" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O66" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P66" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q66" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R66" s="10" t="inlineStr">
@@ -12851,17 +12851,17 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K67" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L67" s="9" t="inlineStr">
@@ -12871,27 +12871,27 @@
       </c>
       <c r="M67" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N67" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R67" s="10" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="K68" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L68" s="9" t="inlineStr">
@@ -12969,17 +12969,17 @@
       </c>
       <c r="O68" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P68" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q68" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R68" s="10" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="S68" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -13037,7 +13037,7 @@
       </c>
       <c r="K69" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L69" s="9" t="inlineStr">
@@ -13057,17 +13057,17 @@
       </c>
       <c r="O69" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P69" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q69" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R69" s="10" t="inlineStr">
@@ -13077,7 +13077,7 @@
       </c>
       <c r="S69" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -13135,27 +13135,27 @@
       </c>
       <c r="M70" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N70" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O70" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P70" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q70" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R70" s="10" t="inlineStr">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="S70" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -13203,12 +13203,12 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K71" s="9" t="inlineStr">
@@ -13223,27 +13223,27 @@
       </c>
       <c r="M71" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N71" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O71" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P71" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q71" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R71" s="10" t="inlineStr">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="S71" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -13291,17 +13291,17 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L72" s="9" t="inlineStr">
@@ -13311,22 +13311,22 @@
       </c>
       <c r="M72" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N72" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O72" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P72" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q72" s="10" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="K73" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L73" s="9" t="inlineStr">
@@ -13409,17 +13409,17 @@
       </c>
       <c r="O73" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P73" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q73" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R73" s="10" t="inlineStr">
@@ -13477,7 +13477,7 @@
       </c>
       <c r="K74" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L74" s="9" t="inlineStr">
@@ -13497,17 +13497,17 @@
       </c>
       <c r="O74" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P74" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q74" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R74" s="10" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="J75" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L75" s="9" t="inlineStr">
@@ -13585,17 +13585,17 @@
       </c>
       <c r="O75" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P75" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q75" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R75" s="10" t="inlineStr">
@@ -13648,12 +13648,12 @@
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K76" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L76" s="9" t="inlineStr">
@@ -13673,12 +13673,12 @@
       </c>
       <c r="O76" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P76" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q76" s="10" t="inlineStr">
@@ -13731,22 +13731,22 @@
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K77" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L77" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M77" s="9" t="inlineStr">
@@ -13761,17 +13761,17 @@
       </c>
       <c r="O77" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P77" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q77" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R77" s="10" t="inlineStr">
@@ -13814,22 +13814,22 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L78" s="9" t="inlineStr">
@@ -13839,27 +13839,27 @@
       </c>
       <c r="M78" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N78" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O78" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P78" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R78" s="10" t="inlineStr">
@@ -13912,12 +13912,12 @@
       </c>
       <c r="J79" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K79" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L79" s="9" t="inlineStr">
@@ -13937,17 +13937,17 @@
       </c>
       <c r="O79" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P79" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q79" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R79" s="10" t="inlineStr">
@@ -13990,7 +13990,7 @@
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I80" s="8" t="inlineStr">
@@ -14005,7 +14005,7 @@
       </c>
       <c r="K80" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L80" s="9" t="inlineStr">
@@ -14025,17 +14025,17 @@
       </c>
       <c r="O80" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P80" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q80" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R80" s="10" t="inlineStr">
@@ -14078,22 +14078,22 @@
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K81" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L81" s="9" t="inlineStr">
@@ -14113,22 +14113,22 @@
       </c>
       <c r="O81" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P81" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q81" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R81" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S81" s="10" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K82" s="9" t="inlineStr">
@@ -14201,17 +14201,17 @@
       </c>
       <c r="O82" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P82" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q82" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R82" s="10" t="inlineStr">
@@ -14254,22 +14254,22 @@
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K83" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L83" s="9" t="inlineStr">
@@ -14289,22 +14289,22 @@
       </c>
       <c r="O83" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P83" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q83" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R83" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S83" s="10" t="inlineStr">
@@ -14342,12 +14342,12 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="K84" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L84" s="9" t="inlineStr">
@@ -14377,22 +14377,22 @@
       </c>
       <c r="O84" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P84" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q84" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R84" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S84" s="10" t="inlineStr">
@@ -14435,12 +14435,12 @@
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K85" s="9" t="inlineStr">
@@ -14455,32 +14455,32 @@
       </c>
       <c r="M85" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N85" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O85" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P85" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q85" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R85" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S85" s="10" t="inlineStr">
@@ -14533,7 +14533,7 @@
       </c>
       <c r="K86" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L86" s="9" t="inlineStr">
@@ -14553,22 +14553,22 @@
       </c>
       <c r="O86" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P86" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q86" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R86" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S86" s="10" t="inlineStr">
@@ -14621,7 +14621,7 @@
       </c>
       <c r="K87" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L87" s="9" t="inlineStr">
@@ -14641,22 +14641,22 @@
       </c>
       <c r="O87" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P87" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q87" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R87" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S87" s="10" t="inlineStr">
@@ -14699,22 +14699,22 @@
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K88" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L88" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M88" s="9" t="inlineStr">
@@ -14734,22 +14734,22 @@
       </c>
       <c r="P88" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q88" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R88" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S88" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -14787,12 +14787,12 @@
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K89" s="9" t="inlineStr">
@@ -14817,22 +14817,22 @@
       </c>
       <c r="O89" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P89" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q89" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R89" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S89" s="10" t="inlineStr">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="K90" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L90" s="9" t="inlineStr">
@@ -14905,17 +14905,17 @@
       </c>
       <c r="O90" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P90" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q90" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R90" s="10" t="inlineStr">

--- a/2designs_codebook.xlsx
+++ b/2designs_codebook.xlsx
@@ -15159,22 +15159,22 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K3" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M3" s="9" t="inlineStr">
@@ -15189,17 +15189,17 @@
       </c>
       <c r="O3" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P3" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" s="10" t="inlineStr">
@@ -15237,7 +15237,7 @@
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
@@ -15335,7 +15335,7 @@
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -15350,7 +15350,7 @@
       </c>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="9" t="inlineStr">
@@ -15360,7 +15360,7 @@
       </c>
       <c r="N5" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" s="10" t="inlineStr">
@@ -15385,7 +15385,7 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -15413,7 +15413,7 @@
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" s="8" t="inlineStr">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" s="9" t="inlineStr">
@@ -15473,7 +15473,7 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -15501,7 +15501,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
@@ -15521,7 +15521,7 @@
       </c>
       <c r="K7" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -15589,7 +15589,7 @@
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -15682,12 +15682,12 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -15702,7 +15702,7 @@
       </c>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" s="9" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="N9" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" s="10" t="inlineStr">
@@ -15737,7 +15737,7 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -15765,7 +15765,7 @@
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -15825,7 +15825,7 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -15956,12 +15956,12 @@
       </c>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" s="9" t="inlineStr">
@@ -15981,7 +15981,7 @@
       </c>
       <c r="O12" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P12" s="10" t="inlineStr">
@@ -16034,17 +16034,17 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" s="9" t="inlineStr">
@@ -16079,7 +16079,7 @@
       </c>
       <c r="Q13" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R13" s="10" t="inlineStr">
@@ -16137,7 +16137,7 @@
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr">
@@ -16298,12 +16298,12 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" s="8" t="inlineStr">
@@ -16318,17 +16318,17 @@
       </c>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O16" s="10" t="inlineStr">
@@ -16338,12 +16338,12 @@
       </c>
       <c r="P16" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q16" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R16" s="10" t="inlineStr">
@@ -16391,17 +16391,17 @@
       </c>
       <c r="I17" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K17" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr">
@@ -16421,17 +16421,17 @@
       </c>
       <c r="O17" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q17" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R17" s="10" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M18" s="9" t="inlineStr">
@@ -16504,7 +16504,7 @@
       </c>
       <c r="N18" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" s="10" t="inlineStr">
@@ -16529,7 +16529,7 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -16567,22 +16567,22 @@
       </c>
       <c r="I19" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" s="9" t="inlineStr">
@@ -16597,17 +16597,17 @@
       </c>
       <c r="O19" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R19" s="10" t="inlineStr">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" s="8" t="inlineStr">
@@ -16670,7 +16670,7 @@
       </c>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M20" s="9" t="inlineStr">
@@ -16680,7 +16680,7 @@
       </c>
       <c r="N20" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O20" s="10" t="inlineStr">
@@ -16705,7 +16705,7 @@
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -16738,22 +16738,22 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr">
@@ -16773,17 +16773,17 @@
       </c>
       <c r="O21" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q21" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R21" s="10" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" s="8" t="inlineStr">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="N22" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O22" s="10" t="inlineStr">
@@ -16881,7 +16881,7 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -16929,7 +16929,7 @@
       </c>
       <c r="K23" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" s="9" t="inlineStr">
@@ -17085,7 +17085,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H25" s="8" t="inlineStr">
@@ -17105,7 +17105,7 @@
       </c>
       <c r="K25" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr">
@@ -17125,7 +17125,7 @@
       </c>
       <c r="O25" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P25" s="10" t="inlineStr">
@@ -17359,12 +17359,12 @@
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="L28" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M28" s="9" t="inlineStr">
@@ -17447,12 +17447,12 @@
       </c>
       <c r="I29" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K29" s="9" t="inlineStr">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="L29" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M29" s="9" t="inlineStr">
@@ -17535,7 +17535,7 @@
       </c>
       <c r="I30" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J30" s="8" t="inlineStr">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="L30" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M30" s="9" t="inlineStr">
@@ -17560,7 +17560,7 @@
       </c>
       <c r="N30" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O30" s="10" t="inlineStr">
@@ -17585,7 +17585,7 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       <c r="F31" s="7" t="n"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="I31" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J31" s="8" t="inlineStr">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -17711,12 +17711,12 @@
       </c>
       <c r="I32" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="L32" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M32" s="9" t="inlineStr">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="P32" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q32" s="10" t="inlineStr">
@@ -17799,7 +17799,7 @@
       </c>
       <c r="I33" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J33" s="8" t="inlineStr">
@@ -17814,7 +17814,7 @@
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M33" s="9" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -17877,7 +17877,7 @@
       <c r="F34" s="7" t="n"/>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -17937,7 +17937,7 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -18063,12 +18063,12 @@
       </c>
       <c r="I36" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -18078,7 +18078,7 @@
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M36" s="9" t="inlineStr">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="P36" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" s="10" t="inlineStr">
@@ -18141,7 +18141,7 @@
       <c r="F37" s="7" t="n"/>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J38" s="8" t="inlineStr">
@@ -18254,7 +18254,7 @@
       </c>
       <c r="L38" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M38" s="9" t="inlineStr">
@@ -18289,7 +18289,7 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -18362,7 +18362,7 @@
       </c>
       <c r="P39" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q39" s="10" t="inlineStr">
@@ -18405,7 +18405,7 @@
       <c r="F40" s="7" t="n"/>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -18498,17 +18498,17 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K41" s="9" t="inlineStr">
@@ -18518,7 +18518,7 @@
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M41" s="9" t="inlineStr">
@@ -18533,17 +18533,17 @@
       </c>
       <c r="O41" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q41" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R41" s="10" t="inlineStr">
@@ -18586,12 +18586,12 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J42" s="8" t="inlineStr">
@@ -18606,7 +18606,7 @@
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M42" s="9" t="inlineStr">
@@ -18616,7 +18616,7 @@
       </c>
       <c r="N42" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O42" s="10" t="inlineStr">
@@ -18626,12 +18626,12 @@
       </c>
       <c r="P42" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q42" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R42" s="10" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I43" s="8" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K43" s="9" t="inlineStr">
@@ -18699,17 +18699,17 @@
       </c>
       <c r="M43" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N43" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O43" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P43" s="10" t="inlineStr">
@@ -18729,7 +18729,7 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -18762,7 +18762,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I44" s="8" t="inlineStr">
@@ -18772,7 +18772,7 @@
       </c>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr">
@@ -18787,12 +18787,12 @@
       </c>
       <c r="M44" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N44" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O44" s="10" t="inlineStr">
@@ -18850,17 +18850,17 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr">
@@ -18875,12 +18875,12 @@
       </c>
       <c r="M45" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N45" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O45" s="10" t="inlineStr">
@@ -18895,7 +18895,7 @@
       </c>
       <c r="Q45" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R45" s="10" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -18933,7 +18933,7 @@
       <c r="F46" s="7" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
@@ -19026,17 +19026,17 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I47" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr">
@@ -19051,12 +19051,12 @@
       </c>
       <c r="M47" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N47" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O47" s="10" t="inlineStr">
@@ -19081,7 +19081,7 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -19114,17 +19114,17 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="L48" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M48" s="9" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="P48" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q48" s="10" t="inlineStr">
@@ -19169,7 +19169,7 @@
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="P49" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q49" s="10" t="inlineStr">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="P50" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q50" s="10" t="inlineStr">
@@ -19373,7 +19373,7 @@
       <c r="F51" s="7" t="n"/>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
@@ -19393,7 +19393,7 @@
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
@@ -19413,12 +19413,12 @@
       </c>
       <c r="O51" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P51" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q51" s="10" t="inlineStr">
@@ -19461,7 +19461,7 @@
       <c r="F52" s="7" t="n"/>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
@@ -19506,7 +19506,7 @@
       </c>
       <c r="P52" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q52" s="10" t="inlineStr">
@@ -19559,17 +19559,17 @@
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K53" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
@@ -19589,12 +19589,12 @@
       </c>
       <c r="O53" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q53" s="10" t="inlineStr">
@@ -19647,12 +19647,12 @@
       </c>
       <c r="I54" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
@@ -19662,7 +19662,7 @@
       </c>
       <c r="L54" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M54" s="9" t="inlineStr">
@@ -19682,7 +19682,7 @@
       </c>
       <c r="P54" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q54" s="10" t="inlineStr">
@@ -19697,7 +19697,7 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -19745,7 +19745,7 @@
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
@@ -19765,17 +19765,17 @@
       </c>
       <c r="O55" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q55" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R55" s="10" t="inlineStr">
@@ -19858,7 +19858,7 @@
       </c>
       <c r="P56" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q56" s="10" t="inlineStr">
@@ -19901,7 +19901,7 @@
       <c r="F57" s="7" t="n"/>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
@@ -19946,7 +19946,7 @@
       </c>
       <c r="P57" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q57" s="10" t="inlineStr">
@@ -19999,12 +19999,12 @@
       </c>
       <c r="I58" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="L58" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M58" s="9" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="P58" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q58" s="10" t="inlineStr">
@@ -20087,7 +20087,7 @@
       </c>
       <c r="I59" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
@@ -20102,7 +20102,7 @@
       </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M59" s="9" t="inlineStr">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="P59" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q59" s="10" t="inlineStr">
@@ -20137,7 +20137,7 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I60" s="8" t="inlineStr">
@@ -20180,7 +20180,7 @@
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
@@ -20195,27 +20195,27 @@
       </c>
       <c r="M60" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N60" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O60" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P60" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q60" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R60" s="10" t="inlineStr">
@@ -20225,7 +20225,7 @@
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -20258,7 +20258,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I61" s="8" t="inlineStr">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="J61" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K61" s="9" t="inlineStr">
@@ -20346,7 +20346,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
@@ -20356,7 +20356,7 @@
       </c>
       <c r="J62" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr">
@@ -20371,12 +20371,12 @@
       </c>
       <c r="M62" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N62" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O62" s="10" t="inlineStr">
@@ -20386,12 +20386,12 @@
       </c>
       <c r="P62" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q62" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R62" s="10" t="inlineStr">
@@ -20401,7 +20401,7 @@
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -20429,7 +20429,7 @@
       <c r="F63" s="7" t="n"/>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
@@ -20522,17 +20522,17 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr">
@@ -20547,12 +20547,12 @@
       </c>
       <c r="M64" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N64" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O64" s="10" t="inlineStr">
@@ -20577,7 +20577,7 @@
       </c>
       <c r="S64" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="I65" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J65" s="8" t="inlineStr">
@@ -20650,12 +20650,12 @@
       </c>
       <c r="P65" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q65" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R65" s="10" t="inlineStr">
@@ -20703,12 +20703,12 @@
       </c>
       <c r="I66" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J66" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
@@ -20718,7 +20718,7 @@
       </c>
       <c r="L66" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M66" s="9" t="inlineStr">
@@ -20733,17 +20733,17 @@
       </c>
       <c r="O66" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P66" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q66" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R66" s="10" t="inlineStr">
@@ -20753,7 +20753,7 @@
       </c>
       <c r="S66" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -20791,12 +20791,12 @@
       </c>
       <c r="I67" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K67" s="9" t="inlineStr">
@@ -20806,7 +20806,7 @@
       </c>
       <c r="L67" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M67" s="9" t="inlineStr">
@@ -20821,17 +20821,17 @@
       </c>
       <c r="O67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R67" s="10" t="inlineStr">
@@ -20841,7 +20841,7 @@
       </c>
       <c r="S67" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -20929,7 +20929,7 @@
       </c>
       <c r="S68" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -21002,7 +21002,7 @@
       </c>
       <c r="P69" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q69" s="10" t="inlineStr">
@@ -21055,12 +21055,12 @@
       </c>
       <c r="I70" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
@@ -21090,7 +21090,7 @@
       </c>
       <c r="P70" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q70" s="10" t="inlineStr">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="S70" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -21143,12 +21143,12 @@
       </c>
       <c r="I71" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K71" s="9" t="inlineStr">
@@ -21158,7 +21158,7 @@
       </c>
       <c r="L71" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M71" s="9" t="inlineStr">
@@ -21168,7 +21168,7 @@
       </c>
       <c r="N71" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O71" s="10" t="inlineStr">
@@ -21178,7 +21178,7 @@
       </c>
       <c r="P71" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q71" s="10" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="S71" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -21231,12 +21231,12 @@
       </c>
       <c r="I72" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J72" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="L72" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M72" s="9" t="inlineStr">
@@ -21266,7 +21266,7 @@
       </c>
       <c r="P72" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q72" s="10" t="inlineStr">
@@ -21281,7 +21281,7 @@
       </c>
       <c r="S72" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -21354,7 +21354,7 @@
       </c>
       <c r="P73" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q73" s="10" t="inlineStr">
@@ -21442,7 +21442,7 @@
       </c>
       <c r="P74" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q74" s="10" t="inlineStr">
@@ -21495,7 +21495,7 @@
       </c>
       <c r="I75" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J75" s="8" t="inlineStr">
@@ -21505,7 +21505,7 @@
       </c>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L75" s="9" t="inlineStr">
@@ -21530,7 +21530,7 @@
       </c>
       <c r="P75" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q75" s="10" t="inlineStr">
@@ -21583,12 +21583,12 @@
       </c>
       <c r="I76" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J76" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K76" s="9" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="L76" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M76" s="9" t="inlineStr">
@@ -21618,7 +21618,7 @@
       </c>
       <c r="P76" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q76" s="10" t="inlineStr">
@@ -21633,7 +21633,7 @@
       </c>
       <c r="S76" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -21666,17 +21666,17 @@
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K77" s="9" t="inlineStr">
@@ -21686,7 +21686,7 @@
       </c>
       <c r="L77" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M77" s="9" t="inlineStr">
@@ -21701,17 +21701,17 @@
       </c>
       <c r="O77" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P77" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q77" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R77" s="10" t="inlineStr">
@@ -21754,12 +21754,12 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
@@ -21774,7 +21774,7 @@
       </c>
       <c r="L78" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M78" s="9" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="N78" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O78" s="10" t="inlineStr">
@@ -21794,12 +21794,12 @@
       </c>
       <c r="P78" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q78" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R78" s="10" t="inlineStr">
@@ -21882,12 +21882,12 @@
       </c>
       <c r="P79" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q79" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R79" s="10" t="inlineStr">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="P80" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q80" s="10" t="inlineStr">
@@ -22018,17 +22018,17 @@
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I81" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K81" s="9" t="inlineStr">
@@ -22038,7 +22038,7 @@
       </c>
       <c r="L81" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M81" s="9" t="inlineStr">
@@ -22053,22 +22053,22 @@
       </c>
       <c r="O81" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P81" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q81" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R81" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S81" s="10" t="inlineStr">
@@ -22101,7 +22101,7 @@
       <c r="F82" s="7" t="n"/>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
@@ -22111,7 +22111,7 @@
       </c>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J82" s="8" t="inlineStr">
@@ -22126,7 +22126,7 @@
       </c>
       <c r="L82" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M82" s="9" t="inlineStr">
@@ -22146,12 +22146,12 @@
       </c>
       <c r="P82" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q82" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R82" s="10" t="inlineStr">
@@ -22194,7 +22194,7 @@
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I83" s="8" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K83" s="9" t="inlineStr">
@@ -22229,17 +22229,17 @@
       </c>
       <c r="O83" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P83" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q83" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R83" s="10" t="inlineStr">
@@ -22282,17 +22282,17 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I84" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J84" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
@@ -22302,7 +22302,7 @@
       </c>
       <c r="L84" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M84" s="9" t="inlineStr">
@@ -22322,17 +22322,17 @@
       </c>
       <c r="P84" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q84" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R84" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S84" s="10" t="inlineStr">
@@ -22370,17 +22370,17 @@
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J85" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K85" s="9" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="L85" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M85" s="9" t="inlineStr">
@@ -22400,7 +22400,7 @@
       </c>
       <c r="N85" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O85" s="10" t="inlineStr">
@@ -22410,17 +22410,17 @@
       </c>
       <c r="P85" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q85" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R85" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S85" s="10" t="inlineStr">
@@ -22586,7 +22586,7 @@
       </c>
       <c r="P87" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q87" s="10" t="inlineStr">
@@ -22639,12 +22639,12 @@
       </c>
       <c r="I88" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K88" s="9" t="inlineStr">
@@ -22654,7 +22654,7 @@
       </c>
       <c r="L88" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M88" s="9" t="inlineStr">
@@ -22684,7 +22684,7 @@
       </c>
       <c r="R88" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S88" s="10" t="inlineStr">
@@ -22722,12 +22722,12 @@
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
@@ -22742,7 +22742,7 @@
       </c>
       <c r="L89" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M89" s="9" t="inlineStr">
@@ -22762,7 +22762,7 @@
       </c>
       <c r="P89" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q89" s="10" t="inlineStr">
@@ -22772,12 +22772,12 @@
       </c>
       <c r="R89" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S89" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -22825,7 +22825,7 @@
       </c>
       <c r="K90" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L90" s="9" t="inlineStr">
